--- a/data/source/weekly/cs-en-us-081pct.xlsx
+++ b/data/source/weekly/cs-en-us-081pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>3</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>200</v>
+      </c>
+      <c r="F15" s="14">
+        <v>3</v>
       </c>
       <c r="G15" s="14">
+        <v>2</v>
+      </c>
+      <c r="H15" s="15">
+        <v>50</v>
+      </c>
+      <c r="I15" s="14">
         <v>3</v>
       </c>
-      <c r="H15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I15" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>-100</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L15" s="15">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="M15" s="15">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="N15" s="15">
-        <v>-100</v>
+        <v>-70</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
+        <v>13</v>
+      </c>
+      <c r="G16" s="14">
+        <v>10</v>
+      </c>
+      <c r="H16" s="15">
+        <v>30</v>
+      </c>
+      <c r="I16" s="14">
+        <v>20</v>
+      </c>
+      <c r="J16" s="14">
         <v>16</v>
       </c>
-      <c r="G16" s="14">
-        <v>7</v>
-      </c>
-      <c r="H16" s="15">
-        <v>128.571428571429</v>
-      </c>
-      <c r="I16" s="14">
-        <v>18</v>
-      </c>
-      <c r="J16" s="14">
-        <v>13</v>
-      </c>
       <c r="K16" s="15">
-        <v>38.461538461538</v>
+        <v>25</v>
       </c>
       <c r="L16" s="15">
-        <v>5.882352941176</v>
+        <v>5.263157894736</v>
       </c>
       <c r="M16" s="15">
-        <v>-53.846153846153</v>
+        <v>-52.380952380952</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.755102040816</v>
+        <v>-87.804878048780</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F17" s="14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G17" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H17" s="15">
-        <v>-15.789473684210</v>
+        <v>23.529411764705</v>
       </c>
       <c r="I17" s="14">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J17" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L17" s="15">
-        <v>-20</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="M17" s="15">
-        <v>-33.333333333333</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="N17" s="15">
-        <v>-71.428571428571</v>
+        <v>-65.263157894736</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1025,31 +1025,31 @@
         <v>-20</v>
       </c>
       <c r="F18" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H18" s="15">
+        <v>-13.333333333333</v>
+      </c>
+      <c r="I18" s="14">
+        <v>24</v>
+      </c>
+      <c r="J18" s="14">
+        <v>20</v>
+      </c>
+      <c r="K18" s="15">
+        <v>20</v>
+      </c>
+      <c r="L18" s="15">
+        <v>50</v>
+      </c>
+      <c r="M18" s="15">
         <v>9.090909090909</v>
       </c>
-      <c r="I18" s="14">
-        <v>19</v>
-      </c>
-      <c r="J18" s="14">
-        <v>15</v>
-      </c>
-      <c r="K18" s="15">
-        <v>26.666666666666</v>
-      </c>
-      <c r="L18" s="15">
-        <v>35.714285714285</v>
-      </c>
-      <c r="M18" s="15">
-        <v>-5</v>
-      </c>
       <c r="N18" s="15">
-        <v>-70.769230769230</v>
+        <v>-67.567567567567</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D19" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>-66.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="F19" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G19" s="14">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="H19" s="15">
-        <v>42.857142857142</v>
+        <v>5.555555555555</v>
       </c>
       <c r="I19" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J19" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="K19" s="15">
-        <v>42.857142857142</v>
+        <v>36</v>
       </c>
       <c r="L19" s="15">
         <v>0</v>
       </c>
       <c r="M19" s="15">
-        <v>30.434782608695</v>
+        <v>25.925925925925</v>
       </c>
       <c r="N19" s="15">
-        <v>-9.090909090909</v>
+        <v>-17.073170731707</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J20" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K20" s="15">
         <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-33.333333333333</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M20" s="15">
         <v>-33.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.666666666666</v>
+        <v>-90.123456790123</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D21" s="17">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>-13.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G21" s="17">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="H21" s="18">
-        <v>15.254237288135</v>
+        <v>12.121212121212</v>
       </c>
       <c r="I21" s="17">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="J21" s="17">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="K21" s="18">
-        <v>12.790697674418</v>
+        <v>17.307692307692</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.960396039603</v>
+        <v>6.086956521739</v>
       </c>
       <c r="M21" s="18">
-        <v>-25.954198473282</v>
+        <v>-20.261437908496</v>
       </c>
       <c r="N21" s="18">
-        <v>-76.570048309178</v>
+        <v>-74.152542372881</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="14">
         <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L22" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="M22" s="15">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D23" s="14">
         <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>-66.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G23" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H23" s="15">
-        <v>-75</v>
+        <v>-40</v>
       </c>
       <c r="I23" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="J23" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K23" s="15">
-        <v>-58.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="L23" s="15">
-        <v>-54.545454545454</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M23" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D24" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E24" s="15">
-        <v>20</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="F24" s="14">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="G24" s="14">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="H24" s="15">
-        <v>24.444444444444</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I24" s="14">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="J24" s="14">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="K24" s="15">
-        <v>30</v>
+        <v>16.438356164383</v>
       </c>
       <c r="L24" s="15">
-        <v>2.631578947368</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="M24" s="15">
-        <v>14.705882352941</v>
+        <v>6.25</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,7 +1303,7 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>20</v>
@@ -1312,25 +1312,25 @@
         <v>21</v>
       </c>
       <c r="F25" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G25" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H25" s="15">
-        <v>175</v>
+        <v>350</v>
       </c>
       <c r="I25" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J25" s="14">
         <v>10</v>
       </c>
       <c r="K25" s="15">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="L25" s="15">
-        <v>55.555555555555</v>
+        <v>41.666666666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>-16.666666666666</v>
+        <v>55.555555555555</v>
       </c>
       <c r="F26" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G26" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="H26" s="15">
-        <v>45.833333333333</v>
+        <v>42.857142857142</v>
       </c>
       <c r="I26" s="14">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="J26" s="14">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="K26" s="15">
-        <v>18.918918918918</v>
+        <v>26.086956521739</v>
       </c>
       <c r="L26" s="15">
-        <v>37.5</v>
+        <v>61.111111111111</v>
       </c>
       <c r="M26" s="15">
-        <v>-47.619047619047</v>
+        <v>-38.947368421052</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>3</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>200</v>
+      </c>
+      <c r="F27" s="14">
+        <v>3</v>
       </c>
       <c r="G27" s="14">
+        <v>2</v>
+      </c>
+      <c r="H27" s="15">
+        <v>50</v>
+      </c>
+      <c r="I27" s="14">
         <v>3</v>
       </c>
-      <c r="H27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I27" s="13" t="s">
-        <v>20</v>
-      </c>
       <c r="J27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>-100</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L27" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1438,10 +1438,10 @@
         <v>1</v>
       </c>
       <c r="G28" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>-83.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I28" s="14">
         <v>3</v>
@@ -1453,7 +1453,7 @@
         <v>-57.142857142857</v>
       </c>
       <c r="L28" s="15">
-        <v>-40</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="14">
         <v>1</v>
       </c>
-      <c r="G29" s="14">
-        <v>2</v>
-      </c>
-      <c r="H29" s="15">
-        <v>-50</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="14">
         <v>1</v>
@@ -1500,7 +1500,7 @@
         <v>-88.888888888888</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.238095238095</v>
+        <v>-95.652173913043</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1519,11 +1519,11 @@
       <c r="F30" s="14">
         <v>1</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>0</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="14">
         <v>1</v>
@@ -1541,7 +1541,7 @@
         <v>-88.888888888888</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.736842105263</v>
+        <v>-95.238095238095</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-081pct.xlsx
+++ b/data/source/weekly/cs-en-us-081pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -895,38 +895,38 @@
       <c r="C15" s="14">
         <v>3</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
+        <v>6</v>
+      </c>
+      <c r="G15" s="14">
         <v>1</v>
       </c>
-      <c r="E15" s="15">
-        <v>200</v>
-      </c>
-      <c r="F15" s="14">
-        <v>3</v>
-      </c>
-      <c r="G15" s="14">
-        <v>2</v>
-      </c>
       <c r="H15" s="15">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J15" s="14">
         <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>-57.142857142857</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L15" s="15">
+        <v>500</v>
+      </c>
+      <c r="M15" s="15">
         <v>200</v>
       </c>
-      <c r="M15" s="15">
-        <v>50</v>
-      </c>
       <c r="N15" s="15">
-        <v>-70</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
         <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>30</v>
+        <v>44.444444444444</v>
       </c>
       <c r="I16" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J16" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K16" s="15">
-        <v>25</v>
+        <v>29.411764705882</v>
       </c>
       <c r="L16" s="15">
-        <v>5.263157894736</v>
+        <v>4.761904761904</v>
       </c>
       <c r="M16" s="15">
-        <v>-52.380952380952</v>
+        <v>-48.837209302325</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.804878048780</v>
+        <v>-87.570621468926</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
         <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G17" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H17" s="15">
-        <v>23.529411764705</v>
+        <v>57.142857142857</v>
       </c>
       <c r="I17" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="J17" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K17" s="15">
-        <v>22.222222222222</v>
+        <v>20</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.333333333333</v>
+        <v>-10</v>
       </c>
       <c r="M17" s="15">
-        <v>-26.666666666666</v>
+        <v>-26.530612244898</v>
       </c>
       <c r="N17" s="15">
-        <v>-65.263157894736</v>
+        <v>-67.567567567567</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-20</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
+        <v>12</v>
+      </c>
+      <c r="G18" s="14">
         <v>13</v>
       </c>
-      <c r="G18" s="14">
-        <v>15</v>
-      </c>
       <c r="H18" s="15">
-        <v>-13.333333333333</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I18" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J18" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K18" s="15">
-        <v>20</v>
+        <v>23.809523809523</v>
       </c>
       <c r="L18" s="15">
-        <v>50</v>
+        <v>52.941176470588</v>
       </c>
       <c r="M18" s="15">
-        <v>9.090909090909</v>
+        <v>8.333333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-67.567567567567</v>
+        <v>-69.411764705882</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>-25</v>
+        <v>12.5</v>
       </c>
       <c r="F19" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G19" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="H19" s="15">
-        <v>5.555555555555</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I19" s="14">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="J19" s="14">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="K19" s="15">
-        <v>36</v>
+        <v>30.303030303030</v>
       </c>
       <c r="L19" s="15">
-        <v>0</v>
+        <v>2.380952380952</v>
       </c>
       <c r="M19" s="15">
-        <v>25.925925925925</v>
+        <v>38.709677419354</v>
       </c>
       <c r="N19" s="15">
-        <v>-17.073170731707</v>
+        <v>-4.444444444444</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="14">
         <v>3</v>
       </c>
-      <c r="D20" s="14">
-        <v>2</v>
-      </c>
       <c r="E20" s="15">
-        <v>50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
         <v>5</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H20" s="15">
-        <v>66.666666666666</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J20" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="L20" s="15">
-        <v>-11.111111111111</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M20" s="15">
         <v>-33.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.123456790123</v>
+        <v>-89.247311827957</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>33.333333333333</v>
+        <v>31.25</v>
       </c>
       <c r="F21" s="17">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="G21" s="17">
         <v>66</v>
       </c>
       <c r="H21" s="18">
-        <v>12.121212121212</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I21" s="17">
-        <v>122</v>
+        <v>143</v>
       </c>
       <c r="J21" s="17">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="K21" s="18">
-        <v>17.307692307692</v>
+        <v>19.166666666666</v>
       </c>
       <c r="L21" s="18">
-        <v>6.086956521739</v>
+        <v>7.518796992481</v>
       </c>
       <c r="M21" s="18">
-        <v>-20.261437908496</v>
+        <v>-14.371257485029</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.152542372881</v>
+        <v>-73.018867924528</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="I22" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J22" s="14">
         <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="L22" s="15">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="M22" s="15">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G23" s="14">
         <v>10</v>
       </c>
       <c r="H23" s="15">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="I23" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J23" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K23" s="15">
-        <v>-40</v>
+        <v>-31.25</v>
       </c>
       <c r="L23" s="15">
-        <v>-30.769230769230</v>
+        <v>-31.25</v>
       </c>
       <c r="M23" s="15">
-        <v>-25</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>13</v>
+      </c>
+      <c r="D24" s="14">
         <v>8</v>
       </c>
-      <c r="D24" s="14">
-        <v>13</v>
-      </c>
       <c r="E24" s="15">
-        <v>-38.461538461538</v>
+        <v>62.5</v>
       </c>
       <c r="F24" s="14">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G24" s="14">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H24" s="15">
-        <v>14.285714285714</v>
+        <v>10</v>
       </c>
       <c r="I24" s="14">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="J24" s="14">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="K24" s="15">
-        <v>16.438356164383</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L24" s="15">
-        <v>-5.555555555555</v>
+        <v>-4.807692307692</v>
       </c>
       <c r="M24" s="15">
-        <v>6.25</v>
+        <v>13.793103448275</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1312,25 +1312,25 @@
         <v>21</v>
       </c>
       <c r="F25" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G25" s="14">
         <v>2</v>
       </c>
       <c r="H25" s="15">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="I25" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J25" s="14">
         <v>10</v>
       </c>
       <c r="K25" s="15">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="L25" s="15">
-        <v>41.666666666666</v>
+        <v>11.764705882352</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E26" s="15">
-        <v>55.555555555555</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="G26" s="14">
         <v>28</v>
       </c>
       <c r="H26" s="15">
-        <v>42.857142857142</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I26" s="14">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="J26" s="14">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K26" s="15">
-        <v>26.086956521739</v>
+        <v>24</v>
       </c>
       <c r="L26" s="15">
-        <v>61.111111111111</v>
+        <v>67.567567567567</v>
       </c>
       <c r="M26" s="15">
-        <v>-38.947368421052</v>
+        <v>-39.805825242718</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="14">
         <v>3</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
+        <v>6</v>
+      </c>
+      <c r="G27" s="14">
         <v>1</v>
       </c>
-      <c r="E27" s="15">
-        <v>200</v>
-      </c>
-      <c r="F27" s="14">
-        <v>3</v>
-      </c>
-      <c r="G27" s="14">
-        <v>2</v>
-      </c>
       <c r="H27" s="15">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="I27" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J27" s="14">
         <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>-57.142857142857</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J28" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K28" s="15">
-        <v>-57.142857142857</v>
+        <v>-37.5</v>
       </c>
       <c r="L28" s="15">
-        <v>-57.142857142857</v>
+        <v>-37.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1500,7 +1500,7 @@
         <v>-88.888888888888</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.652173913043</v>
+        <v>-96.153846153846</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>-88.888888888888</v>
       </c>
       <c r="N30" s="15">
-        <v>-95.238095238095</v>
+        <v>-95.833333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-081pct.xlsx
+++ b/data/source/weekly/cs-en-us-081pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -893,40 +893,40 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>3</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15" s="15">
-        <v>-14.285714285714</v>
+        <v>-12.5</v>
       </c>
       <c r="L15" s="15">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="M15" s="15">
-        <v>200</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N15" s="15">
-        <v>-50</v>
+        <v>-53.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,37 +937,37 @@
         <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G16" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>44.444444444444</v>
+        <v>25</v>
       </c>
       <c r="I16" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J16" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K16" s="15">
-        <v>29.411764705882</v>
+        <v>26.315789473684</v>
       </c>
       <c r="L16" s="15">
-        <v>4.761904761904</v>
+        <v>4.347826086956</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.837209302325</v>
+        <v>-48.936170212766</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.570621468926</v>
+        <v>-87.234042553191</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
         <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G17" s="14">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H17" s="15">
-        <v>57.142857142857</v>
+        <v>61.538461538461</v>
       </c>
       <c r="I17" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J17" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K17" s="15">
-        <v>20</v>
+        <v>21.212121212121</v>
       </c>
       <c r="L17" s="15">
-        <v>-10</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M17" s="15">
-        <v>-26.530612244898</v>
+        <v>-21.568627450980</v>
       </c>
       <c r="N17" s="15">
-        <v>-67.567567567567</v>
+        <v>-66.386554621848</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,13 +1016,13 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
         <v>12</v>
@@ -1034,22 +1034,22 @@
         <v>-7.692307692307</v>
       </c>
       <c r="I18" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J18" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K18" s="15">
-        <v>23.809523809523</v>
+        <v>21.739130434782</v>
       </c>
       <c r="L18" s="15">
-        <v>52.941176470588</v>
+        <v>55.555555555555</v>
       </c>
       <c r="M18" s="15">
-        <v>8.333333333333</v>
+        <v>3.703703703703</v>
       </c>
       <c r="N18" s="15">
-        <v>-69.411764705882</v>
+        <v>-70.526315789473</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>4</v>
+      </c>
+      <c r="D19" s="14">
         <v>9</v>
       </c>
-      <c r="D19" s="14">
-        <v>8</v>
-      </c>
       <c r="E19" s="15">
-        <v>12.5</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F19" s="14">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G19" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H19" s="15">
-        <v>-9.090909090909</v>
+        <v>-29.166666666666</v>
       </c>
       <c r="I19" s="14">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J19" s="14">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="K19" s="15">
-        <v>30.303030303030</v>
+        <v>11.904761904761</v>
       </c>
       <c r="L19" s="15">
-        <v>2.380952380952</v>
+        <v>6.818181818181</v>
       </c>
       <c r="M19" s="15">
-        <v>38.709677419354</v>
+        <v>20.512820512820</v>
       </c>
       <c r="N19" s="15">
-        <v>-4.444444444444</v>
+        <v>-12.962962962963</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1107,31 +1107,31 @@
         <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G20" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H20" s="15">
-        <v>-16.666666666666</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I20" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J20" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K20" s="15">
-        <v>-9.090909090909</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L20" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M20" s="15">
-        <v>-33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.247311827957</v>
+        <v>-88.571428571428</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>31.25</v>
+        <v>-30</v>
       </c>
       <c r="F21" s="17">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="G21" s="17">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H21" s="18">
-        <v>18.181818181818</v>
+        <v>7.246376811594</v>
       </c>
       <c r="I21" s="17">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="J21" s="17">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="K21" s="18">
-        <v>19.166666666666</v>
+        <v>12.857142857142</v>
       </c>
       <c r="L21" s="18">
-        <v>7.518796992481</v>
+        <v>7.482993197278</v>
       </c>
       <c r="M21" s="18">
-        <v>-14.371257485029</v>
+        <v>-15.053763440860</v>
       </c>
       <c r="N21" s="18">
-        <v>-73.018867924528</v>
+        <v>-72.898799313893</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>2</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,13 +1189,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>6</v>
-      </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>500</v>
+        <v>5</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>7</v>
@@ -1210,7 +1210,7 @@
         <v>250</v>
       </c>
       <c r="M22" s="15">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
-        <v>2</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G23" s="14">
         <v>10</v>
       </c>
       <c r="H23" s="15">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="I23" s="14">
         <v>11</v>
       </c>
       <c r="J23" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K23" s="15">
-        <v>-31.25</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="L23" s="15">
-        <v>-31.25</v>
+        <v>-35.294117647058</v>
       </c>
       <c r="M23" s="15">
-        <v>-8.333333333333</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D24" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E24" s="15">
-        <v>62.5</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F24" s="14">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G24" s="14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H24" s="15">
-        <v>10</v>
+        <v>2.380952380952</v>
       </c>
       <c r="I24" s="14">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="J24" s="14">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="K24" s="15">
-        <v>22.222222222222</v>
+        <v>16.304347826087</v>
       </c>
       <c r="L24" s="15">
-        <v>-4.807692307692</v>
+        <v>-6.956521739130</v>
       </c>
       <c r="M24" s="15">
-        <v>13.793103448275</v>
+        <v>1.904761904761</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,7 +1303,7 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>20</v>
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="F25" s="14">
-        <v>10</v>
-      </c>
-      <c r="G25" s="14">
-        <v>2</v>
-      </c>
-      <c r="H25" s="15">
-        <v>400</v>
+        <v>6</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I25" s="14">
         <v>19</v>
@@ -1330,7 +1330,7 @@
         <v>90</v>
       </c>
       <c r="L25" s="15">
-        <v>11.764705882352</v>
+        <v>5.555555555555</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="F26" s="14">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G26" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H26" s="15">
-        <v>14.285714285714</v>
+        <v>6.896551724137</v>
       </c>
       <c r="I26" s="14">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="J26" s="14">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K26" s="15">
-        <v>24</v>
+        <v>18.333333333333</v>
       </c>
       <c r="L26" s="15">
-        <v>67.567567567567</v>
+        <v>51.063829787234</v>
       </c>
       <c r="M26" s="15">
-        <v>-39.805825242718</v>
+        <v>-36.607142857142</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,34 +1385,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>3</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>-14.285714285714</v>
+        <v>-12.5</v>
       </c>
       <c r="L27" s="15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>2</v>
-      </c>
-      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="E28" s="15">
-        <v>100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" s="14">
         <v>8</v>
       </c>
       <c r="K28" s="15">
-        <v>-37.5</v>
+        <v>-25</v>
       </c>
       <c r="L28" s="15">
-        <v>-37.5</v>
+        <v>-25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1485,30 +1485,30 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="14">
         <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M29" s="15">
-        <v>-88.888888888888</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="N29" s="15">
-        <v>-96.153846153846</v>
+        <v>-92.857142857142</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1526,22 +1526,22 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M30" s="15">
-        <v>-88.888888888888</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="N30" s="15">
-        <v>-95.833333333333</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-081pct.xlsx
+++ b/data/source/weekly/cs-en-us-081pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -854,26 +854,26 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
       </c>
       <c r="J14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="15">
         <v>-100</v>
@@ -902,72 +902,72 @@
         <v>0</v>
       </c>
       <c r="F15" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>250</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>-12.5</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L15" s="15">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="M15" s="15">
-        <v>133.333333333333</v>
+        <v>166.666666666667</v>
       </c>
       <c r="N15" s="15">
-        <v>-53.333333333333</v>
+        <v>-55.555555555555</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>2</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>25</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I16" s="14">
         <v>24</v>
       </c>
       <c r="J16" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K16" s="15">
-        <v>26.315789473684</v>
+        <v>20</v>
       </c>
       <c r="L16" s="15">
-        <v>4.347826086956</v>
+        <v>-4</v>
       </c>
       <c r="M16" s="15">
-        <v>-48.936170212766</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.234042553191</v>
+        <v>-88.785046728972</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E17" s="15">
-        <v>33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G17" s="14">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="H17" s="15">
-        <v>61.538461538461</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I17" s="14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J17" s="14">
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="K17" s="15">
-        <v>21.212121212121</v>
+        <v>4.761904761904</v>
       </c>
       <c r="L17" s="15">
-        <v>-16.666666666666</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="M17" s="15">
-        <v>-21.568627450980</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="N17" s="15">
-        <v>-66.386554621848</v>
+        <v>-66.917293233082</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H18" s="15">
-        <v>-7.692307692307</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="I18" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J18" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K18" s="15">
-        <v>21.739130434782</v>
+        <v>15.384615384615</v>
       </c>
       <c r="L18" s="15">
-        <v>55.555555555555</v>
+        <v>57.894736842105</v>
       </c>
       <c r="M18" s="15">
-        <v>3.703703703703</v>
+        <v>-3.225806451612</v>
       </c>
       <c r="N18" s="15">
-        <v>-70.526315789473</v>
+        <v>-73.451327433628</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>8</v>
+      </c>
+      <c r="D19" s="14">
         <v>4</v>
       </c>
-      <c r="D19" s="14">
-        <v>9</v>
-      </c>
       <c r="E19" s="15">
-        <v>-55.555555555555</v>
+        <v>100</v>
       </c>
       <c r="F19" s="14">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G19" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H19" s="15">
-        <v>-29.166666666666</v>
+        <v>-8</v>
       </c>
       <c r="I19" s="14">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="J19" s="14">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="K19" s="15">
-        <v>11.904761904761</v>
+        <v>19.565217391304</v>
       </c>
       <c r="L19" s="15">
-        <v>6.818181818181</v>
+        <v>12.244897959183</v>
       </c>
       <c r="M19" s="15">
-        <v>20.512820512820</v>
+        <v>25</v>
       </c>
       <c r="N19" s="15">
-        <v>-12.962962962963</v>
+        <v>-11.290322580645</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
         <v>2</v>
       </c>
-      <c r="D20" s="14">
-        <v>3</v>
-      </c>
       <c r="E20" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G20" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H20" s="15">
-        <v>-22.222222222222</v>
+        <v>-20</v>
       </c>
       <c r="I20" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J20" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K20" s="15">
-        <v>-14.285714285714</v>
+        <v>-18.75</v>
       </c>
       <c r="L20" s="15">
         <v>0</v>
       </c>
       <c r="M20" s="15">
-        <v>-20</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.571428571428</v>
+        <v>-89.075630252100</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-30</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F21" s="17">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G21" s="17">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="H21" s="18">
-        <v>7.246376811594</v>
+        <v>0</v>
       </c>
       <c r="I21" s="17">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="J21" s="17">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="K21" s="18">
-        <v>12.857142857142</v>
+        <v>8.074534161490</v>
       </c>
       <c r="L21" s="18">
-        <v>7.482993197278</v>
+        <v>7.407407407407</v>
       </c>
       <c r="M21" s="18">
-        <v>-15.053763440860</v>
+        <v>-15.533980582524</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.898799313893</v>
+        <v>-73.873873873873</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>-25</v>
       </c>
       <c r="F23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G23" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H23" s="15">
-        <v>-30</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I23" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J23" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K23" s="15">
-        <v>-42.105263157894</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="L23" s="15">
-        <v>-35.294117647058</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="M23" s="15">
-        <v>-15.384615384615</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D24" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E24" s="15">
-        <v>-9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G24" s="14">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H24" s="15">
-        <v>2.380952380952</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="J24" s="14">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="K24" s="15">
-        <v>16.304347826087</v>
+        <v>16.346153846153</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.956521739130</v>
+        <v>-6.201550387596</v>
       </c>
       <c r="M24" s="15">
-        <v>1.904761904761</v>
+        <v>1.680672268907</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1321,16 +1321,16 @@
         <v>21</v>
       </c>
       <c r="I25" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J25" s="14">
         <v>10</v>
       </c>
       <c r="K25" s="15">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="L25" s="15">
-        <v>5.555555555555</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>-10</v>
+        <v>133.333333333333</v>
       </c>
       <c r="F26" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G26" s="14">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H26" s="15">
-        <v>6.896551724137</v>
+        <v>26.923076923076</v>
       </c>
       <c r="I26" s="14">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="J26" s="14">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K26" s="15">
-        <v>18.333333333333</v>
+        <v>23.809523809523</v>
       </c>
       <c r="L26" s="15">
-        <v>51.063829787234</v>
+        <v>47.169811320754</v>
       </c>
       <c r="M26" s="15">
-        <v>-36.607142857142</v>
+        <v>-39.0625</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1388,31 +1388,31 @@
         <v>1</v>
       </c>
       <c r="D27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K27" s="15">
-        <v>-12.5</v>
+        <v>-20</v>
       </c>
       <c r="L27" s="15">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
         <v>1</v>
       </c>
       <c r="H28" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="I28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J28" s="14">
         <v>8</v>
       </c>
       <c r="K28" s="15">
-        <v>-25</v>
+        <v>-12.5</v>
       </c>
       <c r="L28" s="15">
-        <v>-25</v>
+        <v>-12.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1497,18 +1497,18 @@
         <v>21</v>
       </c>
       <c r="M29" s="15">
-        <v>-77.777777777777</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="N29" s="15">
-        <v>-92.857142857142</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1538,10 +1538,10 @@
         <v>21</v>
       </c>
       <c r="M30" s="15">
-        <v>-77.777777777777</v>
+        <v>-80</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.307692307692</v>
+        <v>-93.548387096774</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-081pct.xlsx
+++ b/data/source/weekly/cs-en-us-081pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -878,8 +878,8 @@
       <c r="K14" s="15">
         <v>-100</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>21</v>
+      <c r="L14" s="15">
+        <v>-100</v>
       </c>
       <c r="M14" s="15">
         <v>-100</v>
@@ -892,82 +892,82 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>0</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>166.666666666667</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J15" s="14">
         <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>-11.111111111111</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L15" s="15">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="M15" s="15">
-        <v>166.666666666667</v>
+        <v>40</v>
       </c>
       <c r="N15" s="15">
-        <v>-55.555555555555</v>
+        <v>-65</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
         <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J16" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K16" s="15">
-        <v>20</v>
+        <v>18.181818181818</v>
       </c>
       <c r="L16" s="15">
-        <v>-4</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M16" s="15">
-        <v>-53.846153846153</v>
+        <v>-52.727272727272</v>
       </c>
       <c r="N16" s="15">
-        <v>-88.785046728972</v>
+        <v>-89.121338912133</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>6</v>
+      </c>
+      <c r="D17" s="14">
         <v>3</v>
       </c>
-      <c r="D17" s="14">
-        <v>9</v>
-      </c>
       <c r="E17" s="15">
-        <v>-66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F17" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G17" s="14">
         <v>18</v>
       </c>
       <c r="H17" s="15">
-        <v>11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J17" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="K17" s="15">
-        <v>4.761904761904</v>
+        <v>15.555555555555</v>
       </c>
       <c r="L17" s="15">
-        <v>-18.518518518518</v>
+        <v>-16.129032258064</v>
       </c>
       <c r="M17" s="15">
-        <v>-18.518518518518</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="N17" s="15">
-        <v>-66.917293233082</v>
+        <v>-65.333333333333</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
         <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F18" s="14">
         <v>10</v>
       </c>
       <c r="G18" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H18" s="15">
-        <v>-9.090909090909</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I18" s="14">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J18" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K18" s="15">
-        <v>15.384615384615</v>
+        <v>17.241379310344</v>
       </c>
       <c r="L18" s="15">
-        <v>57.894736842105</v>
+        <v>61.904761904761</v>
       </c>
       <c r="M18" s="15">
-        <v>-3.225806451612</v>
+        <v>0</v>
       </c>
       <c r="N18" s="15">
-        <v>-73.451327433628</v>
+        <v>-73.228346456692</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>100</v>
+        <v>-40</v>
       </c>
       <c r="F19" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G19" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H19" s="15">
-        <v>-8</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I19" s="14">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="J19" s="14">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="K19" s="15">
-        <v>19.565217391304</v>
+        <v>13.725490196078</v>
       </c>
       <c r="L19" s="15">
-        <v>12.244897959183</v>
+        <v>5.454545454545</v>
       </c>
       <c r="M19" s="15">
-        <v>25</v>
+        <v>5.454545454545</v>
       </c>
       <c r="N19" s="15">
-        <v>-11.290322580645</v>
+        <v>-12.121212121212</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,13 +1098,13 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D20" s="14">
         <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
         <v>8</v>
@@ -1116,22 +1116,22 @@
         <v>-20</v>
       </c>
       <c r="I20" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J20" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K20" s="15">
-        <v>-18.75</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L20" s="15">
         <v>0</v>
       </c>
       <c r="M20" s="15">
-        <v>-23.529411764705</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.075630252100</v>
+        <v>-87.401574803149</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>19</v>
+      </c>
+      <c r="D21" s="17">
         <v>15</v>
       </c>
-      <c r="D21" s="17">
-        <v>21</v>
-      </c>
       <c r="E21" s="18">
-        <v>-28.571428571428</v>
+        <v>26.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G21" s="17">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="H21" s="18">
-        <v>0</v>
+        <v>-2.777777777777</v>
       </c>
       <c r="I21" s="17">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="J21" s="17">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="K21" s="18">
-        <v>8.074534161490</v>
+        <v>9.659090909090</v>
       </c>
       <c r="L21" s="18">
-        <v>7.407407407407</v>
+        <v>4.324324324324</v>
       </c>
       <c r="M21" s="18">
-        <v>-15.533980582524</v>
+        <v>-17.167381974248</v>
       </c>
       <c r="N21" s="18">
-        <v>-73.873873873873</v>
+        <v>-73.777173913043</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,32 +1182,32 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>2</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="G22" s="14">
+        <v>2</v>
+      </c>
+      <c r="H22" s="15">
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>7</v>
       </c>
       <c r="J22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K22" s="15">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="L22" s="15">
-        <v>250</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M22" s="15">
         <v>250</v>
@@ -1223,35 +1223,35 @@
       <c r="C23" s="14">
         <v>3</v>
       </c>
-      <c r="D23" s="14">
-        <v>4</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-25</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
         <v>8</v>
       </c>
       <c r="G23" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H23" s="15">
-        <v>-27.272727272727</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J23" s="14">
         <v>23</v>
       </c>
       <c r="K23" s="15">
-        <v>-43.478260869565</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="L23" s="15">
-        <v>-27.777777777777</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="M23" s="15">
-        <v>-13.333333333333</v>
+        <v>0</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D24" s="14">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>44.444444444444</v>
       </c>
       <c r="F24" s="14">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G24" s="14">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="H24" s="15">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="I24" s="14">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="J24" s="14">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="K24" s="15">
-        <v>16.346153846153</v>
+        <v>17.699115044247</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.201550387596</v>
+        <v>-2.919708029197</v>
       </c>
       <c r="M24" s="15">
-        <v>1.680672268907</v>
+        <v>-2.205882352941</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1312,7 +1312,7 @@
         <v>21</v>
       </c>
       <c r="F25" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>20</v>
@@ -1321,16 +1321,16 @@
         <v>21</v>
       </c>
       <c r="I25" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J25" s="14">
         <v>10</v>
       </c>
       <c r="K25" s="15">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="L25" s="15">
-        <v>-13.043478260869</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D26" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>133.333333333333</v>
+        <v>216.666666666667</v>
       </c>
       <c r="F26" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G26" s="14">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="H26" s="15">
-        <v>26.923076923076</v>
+        <v>65.217391304347</v>
       </c>
       <c r="I26" s="14">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="J26" s="14">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="K26" s="15">
-        <v>23.809523809523</v>
+        <v>39.130434782608</v>
       </c>
       <c r="L26" s="15">
-        <v>47.169811320754</v>
+        <v>54.838709677419</v>
       </c>
       <c r="M26" s="15">
-        <v>-39.0625</v>
+        <v>-31.428571428571</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
-      </c>
-      <c r="D27" s="14">
-        <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-50</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J27" s="14">
         <v>10</v>
       </c>
       <c r="K27" s="15">
-        <v>-20</v>
+        <v>-30</v>
       </c>
       <c r="L27" s="15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="15">
+        <v>100</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="I28" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K28" s="15">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>-12.5</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1493,14 +1493,14 @@
       <c r="K29" s="15">
         <v>0</v>
       </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
+      <c r="L29" s="15">
+        <v>-33.333333333333</v>
       </c>
       <c r="M29" s="15">
         <v>-81.818181818181</v>
       </c>
       <c r="N29" s="15">
-        <v>-94.117647058823</v>
+        <v>-95.121951219512</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1534,14 +1534,14 @@
       <c r="K30" s="15">
         <v>100</v>
       </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
+      <c r="L30" s="15">
+        <v>0</v>
       </c>
       <c r="M30" s="15">
         <v>-80</v>
       </c>
       <c r="N30" s="15">
-        <v>-93.548387096774</v>
+        <v>-94.594594594594</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-081pct.xlsx
+++ b/data/source/weekly/cs-en-us-081pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -902,13 +902,13 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G15" s="14">
         <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>7</v>
@@ -920,13 +920,13 @@
         <v>-22.222222222222</v>
       </c>
       <c r="L15" s="15">
-        <v>250</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M15" s="15">
-        <v>40</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N15" s="15">
-        <v>-65</v>
+        <v>-68.181818181818</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
         <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" s="14">
         <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J16" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K16" s="15">
-        <v>18.181818181818</v>
+        <v>17.391304347826</v>
       </c>
       <c r="L16" s="15">
-        <v>-7.142857142857</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="M16" s="15">
-        <v>-52.727272727272</v>
+        <v>-54.237288135593</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.121338912133</v>
+        <v>-89.575289575289</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>9</v>
+      </c>
+      <c r="D17" s="14">
         <v>6</v>
       </c>
-      <c r="D17" s="14">
-        <v>3</v>
-      </c>
       <c r="E17" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H17" s="15">
+        <v>14.285714285714</v>
+      </c>
+      <c r="I17" s="14">
+        <v>61</v>
+      </c>
+      <c r="J17" s="14">
+        <v>51</v>
+      </c>
+      <c r="K17" s="15">
+        <v>19.607843137254</v>
+      </c>
+      <c r="L17" s="15">
+        <v>-6.153846153846</v>
+      </c>
+      <c r="M17" s="15">
         <v>0</v>
       </c>
-      <c r="I17" s="14">
-        <v>52</v>
-      </c>
-      <c r="J17" s="14">
-        <v>45</v>
-      </c>
-      <c r="K17" s="15">
-        <v>15.555555555555</v>
-      </c>
-      <c r="L17" s="15">
-        <v>-16.129032258064</v>
-      </c>
-      <c r="M17" s="15">
-        <v>-13.333333333333</v>
-      </c>
       <c r="N17" s="15">
-        <v>-65.333333333333</v>
+        <v>-62.576687116564</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
+        <v>8</v>
+      </c>
+      <c r="G18" s="14">
         <v>10</v>
       </c>
-      <c r="G18" s="14">
-        <v>9</v>
-      </c>
       <c r="H18" s="15">
-        <v>11.111111111111</v>
+        <v>-20</v>
       </c>
       <c r="I18" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J18" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K18" s="15">
-        <v>17.241379310344</v>
+        <v>16.129032258064</v>
       </c>
       <c r="L18" s="15">
-        <v>61.904761904761</v>
+        <v>63.636363636363</v>
       </c>
       <c r="M18" s="15">
-        <v>0</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="N18" s="15">
-        <v>-73.228346456692</v>
+        <v>-74.100719424460</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E19" s="15">
-        <v>-40</v>
+        <v>700</v>
       </c>
       <c r="F19" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G19" s="14">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="H19" s="15">
-        <v>-7.692307692307</v>
+        <v>21.052631578947</v>
       </c>
       <c r="I19" s="14">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="J19" s="14">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K19" s="15">
-        <v>13.725490196078</v>
+        <v>26.923076923076</v>
       </c>
       <c r="L19" s="15">
-        <v>5.454545454545</v>
+        <v>11.864406779661</v>
       </c>
       <c r="M19" s="15">
-        <v>5.454545454545</v>
+        <v>11.864406779661</v>
       </c>
       <c r="N19" s="15">
-        <v>-12.121212121212</v>
+        <v>-9.589041095890</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,10 +1098,10 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
         <v>100</v>
@@ -1110,28 +1110,28 @@
         <v>8</v>
       </c>
       <c r="G20" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H20" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J20" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K20" s="15">
-        <v>-11.111111111111</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="L20" s="15">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="M20" s="15">
-        <v>-15.789473684210</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.401574803149</v>
+        <v>-87.412587412587</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D21" s="17">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E21" s="18">
-        <v>26.666666666666</v>
+        <v>90.909090909090</v>
       </c>
       <c r="F21" s="17">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G21" s="17">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H21" s="18">
-        <v>-2.777777777777</v>
+        <v>2.985074626865</v>
       </c>
       <c r="I21" s="17">
-        <v>193</v>
+        <v>215</v>
       </c>
       <c r="J21" s="17">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="K21" s="18">
-        <v>9.659090909090</v>
+        <v>14.973262032085</v>
       </c>
       <c r="L21" s="18">
-        <v>4.324324324324</v>
+        <v>10.256410256410</v>
       </c>
       <c r="M21" s="18">
-        <v>-17.167381974248</v>
+        <v>-14.342629482071</v>
       </c>
       <c r="N21" s="18">
-        <v>-73.777173913043</v>
+        <v>-73.325062034739</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,20 +1182,20 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="14">
-        <v>2</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G22" s="14">
         <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>7</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>2</v>
+      </c>
+      <c r="D23" s="14">
         <v>3</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="E23" s="15">
+        <v>-33.333333333333</v>
       </c>
       <c r="F23" s="14">
         <v>8</v>
       </c>
       <c r="G23" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="I23" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J23" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K23" s="15">
-        <v>-30.434782608695</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="L23" s="15">
-        <v>-23.809523809523</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="M23" s="15">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D24" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E24" s="15">
-        <v>44.444444444444</v>
+        <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G24" s="14">
         <v>40</v>
       </c>
       <c r="H24" s="15">
-        <v>17.5</v>
+        <v>10</v>
       </c>
       <c r="I24" s="14">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="J24" s="14">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="K24" s="15">
-        <v>17.699115044247</v>
+        <v>15.702479338843</v>
       </c>
       <c r="L24" s="15">
-        <v>-2.919708029197</v>
+        <v>-10.828025477707</v>
       </c>
       <c r="M24" s="15">
-        <v>-2.205882352941</v>
+        <v>-5.405405405405</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="14">
+      <c r="C25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="14">
         <v>1</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>21</v>
+      <c r="E25" s="15">
+        <v>-100</v>
       </c>
       <c r="F25" s="14">
-        <v>5</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="G25" s="14">
+        <v>1</v>
+      </c>
+      <c r="H25" s="15">
+        <v>200</v>
       </c>
       <c r="I25" s="14">
         <v>21</v>
       </c>
       <c r="J25" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K25" s="15">
-        <v>110</v>
+        <v>90.909090909090</v>
       </c>
       <c r="L25" s="15">
-        <v>-22.222222222222</v>
+        <v>-30</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>216.666666666667</v>
+        <v>22.222222222222</v>
       </c>
       <c r="F26" s="14">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G26" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="H26" s="15">
-        <v>65.217391304347</v>
+        <v>57.142857142857</v>
       </c>
       <c r="I26" s="14">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="J26" s="14">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="K26" s="15">
-        <v>39.130434782608</v>
+        <v>35.897435897435</v>
       </c>
       <c r="L26" s="15">
-        <v>54.838709677419</v>
+        <v>60.606060606060</v>
       </c>
       <c r="M26" s="15">
-        <v>-31.428571428571</v>
+        <v>-30.718954248366</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,13 +1394,13 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G27" s="14">
         <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="14">
         <v>7</v>
@@ -1412,7 +1412,7 @@
         <v>-30</v>
       </c>
       <c r="L27" s="15">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>2</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="14">
         <v>1</v>
       </c>
       <c r="E28" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I28" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="L28" s="15">
-        <v>-18.181818181818</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="C29" s="14">
+        <v>4</v>
+      </c>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>300</v>
       </c>
       <c r="F29" s="14">
+        <v>5</v>
+      </c>
+      <c r="G29" s="14">
         <v>1</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="H29" s="15">
+        <v>400</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29" s="15">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="M29" s="15">
-        <v>-81.818181818181</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="N29" s="15">
-        <v>-95.121951219512</v>
+        <v>-85.714285714285</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="C30" s="14">
+        <v>3</v>
+      </c>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>200</v>
       </c>
       <c r="F30" s="14">
+        <v>4</v>
+      </c>
+      <c r="G30" s="14">
         <v>1</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="H30" s="15">
+        <v>300</v>
       </c>
       <c r="I30" s="14">
+        <v>5</v>
+      </c>
+      <c r="J30" s="14">
         <v>2</v>
       </c>
-      <c r="J30" s="14">
-        <v>1</v>
-      </c>
       <c r="K30" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="L30" s="15">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="M30" s="15">
-        <v>-80</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-94.594594594594</v>
+        <v>-86.842105263157</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-081pct.xlsx
+++ b/data/source/weekly/cs-en-us-081pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -905,10 +905,10 @@
         <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="14">
         <v>7</v>
@@ -920,10 +920,10 @@
         <v>-22.222222222222</v>
       </c>
       <c r="L15" s="15">
-        <v>133.333333333333</v>
+        <v>75</v>
       </c>
       <c r="M15" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
         <v>-68.181818181818</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F16" s="14">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H16" s="15">
-        <v>-16.666666666666</v>
+        <v>85.714285714285</v>
       </c>
       <c r="I16" s="14">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="J16" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K16" s="15">
-        <v>17.391304347826</v>
+        <v>42.307692307692</v>
       </c>
       <c r="L16" s="15">
-        <v>-6.896551724137</v>
+        <v>19.354838709677</v>
       </c>
       <c r="M16" s="15">
-        <v>-54.237288135593</v>
+        <v>-41.269841269841</v>
       </c>
       <c r="N16" s="15">
-        <v>-89.575289575289</v>
+        <v>-86.738351254480</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
         <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H17" s="15">
-        <v>14.285714285714</v>
+        <v>4.347826086956</v>
       </c>
       <c r="I17" s="14">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="J17" s="14">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="K17" s="15">
-        <v>19.607843137254</v>
+        <v>16.071428571428</v>
       </c>
       <c r="L17" s="15">
-        <v>-6.153846153846</v>
+        <v>-5.797101449275</v>
       </c>
       <c r="M17" s="15">
-        <v>0</v>
+        <v>-2.985074626865</v>
       </c>
       <c r="N17" s="15">
-        <v>-62.576687116564</v>
+        <v>-63.687150837988</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
-      </c>
-      <c r="D18" s="14">
         <v>2</v>
       </c>
-      <c r="E18" s="15">
-        <v>-50</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
+        <v>9</v>
+      </c>
+      <c r="G18" s="14">
         <v>8</v>
       </c>
-      <c r="G18" s="14">
-        <v>10</v>
-      </c>
       <c r="H18" s="15">
-        <v>-20</v>
+        <v>12.5</v>
       </c>
       <c r="I18" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="J18" s="14">
         <v>31</v>
       </c>
       <c r="K18" s="15">
-        <v>16.129032258064</v>
+        <v>22.580645161290</v>
       </c>
       <c r="L18" s="15">
-        <v>63.636363636363</v>
+        <v>65.217391304347</v>
       </c>
       <c r="M18" s="15">
-        <v>-7.692307692307</v>
+        <v>-11.627906976744</v>
       </c>
       <c r="N18" s="15">
-        <v>-74.100719424460</v>
+        <v>-75</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>700</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="14">
         <v>23</v>
       </c>
       <c r="G19" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H19" s="15">
-        <v>21.052631578947</v>
+        <v>43.75</v>
       </c>
       <c r="I19" s="14">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="J19" s="14">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="K19" s="15">
-        <v>26.923076923076</v>
+        <v>20.689655172413</v>
       </c>
       <c r="L19" s="15">
-        <v>11.864406779661</v>
+        <v>12.903225806451</v>
       </c>
       <c r="M19" s="15">
-        <v>11.864406779661</v>
+        <v>7.692307692307</v>
       </c>
       <c r="N19" s="15">
-        <v>-9.589041095890</v>
+        <v>-14.634146341463</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
         <v>2</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
         <v>8</v>
       </c>
       <c r="G20" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H20" s="15">
+        <v>14.285714285714</v>
+      </c>
+      <c r="I20" s="14">
+        <v>19</v>
+      </c>
+      <c r="J20" s="14">
+        <v>21</v>
+      </c>
+      <c r="K20" s="15">
+        <v>-9.523809523809</v>
+      </c>
+      <c r="L20" s="15">
         <v>0</v>
       </c>
-      <c r="I20" s="14">
-        <v>18</v>
-      </c>
-      <c r="J20" s="14">
-        <v>19</v>
-      </c>
-      <c r="K20" s="15">
-        <v>-5.263157894736</v>
-      </c>
-      <c r="L20" s="15">
-        <v>12.5</v>
-      </c>
       <c r="M20" s="15">
-        <v>-18.181818181818</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.412587412587</v>
+        <v>-87.333333333333</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>90.909090909090</v>
+        <v>25</v>
       </c>
       <c r="F21" s="17">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="G21" s="17">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="H21" s="18">
-        <v>2.985074626865</v>
+        <v>23.809523809523</v>
       </c>
       <c r="I21" s="17">
-        <v>215</v>
+        <v>236</v>
       </c>
       <c r="J21" s="17">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="K21" s="18">
-        <v>14.973262032085</v>
+        <v>16.256157635468</v>
       </c>
       <c r="L21" s="18">
-        <v>10.256410256410</v>
+        <v>12.918660287081</v>
       </c>
       <c r="M21" s="18">
-        <v>-14.342629482071</v>
+        <v>-13.553113553113</v>
       </c>
       <c r="N21" s="18">
-        <v>-73.325062034739</v>
+        <v>-72.904707233065</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,17 +1182,17 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H22" s="15">
         <v>-100</v>
@@ -1201,16 +1201,16 @@
         <v>7</v>
       </c>
       <c r="J22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22" s="15">
+        <v>40</v>
+      </c>
+      <c r="L22" s="15">
         <v>75</v>
       </c>
-      <c r="L22" s="15">
-        <v>133.333333333333</v>
-      </c>
       <c r="M22" s="15">
-        <v>250</v>
+        <v>75</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="F23" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G23" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H23" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="I23" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J23" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="K23" s="15">
-        <v>-30.769230769230</v>
+        <v>-30</v>
       </c>
       <c r="L23" s="15">
-        <v>-18.181818181818</v>
+        <v>-12.5</v>
       </c>
       <c r="M23" s="15">
-        <v>-10</v>
+        <v>5</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D24" s="14">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E24" s="15">
         <v>0</v>
       </c>
       <c r="F24" s="14">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G24" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="H24" s="15">
-        <v>10</v>
+        <v>9.302325581395</v>
       </c>
       <c r="I24" s="14">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="J24" s="14">
-        <v>121</v>
+        <v>135</v>
       </c>
       <c r="K24" s="15">
-        <v>15.702479338843</v>
+        <v>14.814814814814</v>
       </c>
       <c r="L24" s="15">
-        <v>-10.828025477707</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="M24" s="15">
-        <v>-5.405405405405</v>
+        <v>0.649350649350</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
+      <c r="C25" s="14">
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
+        <v>5</v>
+      </c>
+      <c r="G25" s="14">
         <v>3</v>
       </c>
-      <c r="G25" s="14">
-        <v>1</v>
-      </c>
       <c r="H25" s="15">
-        <v>200</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J25" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K25" s="15">
-        <v>90.909090909090</v>
+        <v>84.615384615384</v>
       </c>
       <c r="L25" s="15">
-        <v>-30</v>
+        <v>-25</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>22.222222222222</v>
+        <v>80</v>
       </c>
       <c r="F26" s="14">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G26" s="14">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H26" s="15">
-        <v>57.142857142857</v>
+        <v>95.652173913043</v>
       </c>
       <c r="I26" s="14">
-        <v>106</v>
+        <v>116</v>
       </c>
       <c r="J26" s="14">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="K26" s="15">
-        <v>35.897435897435</v>
+        <v>39.759036144578</v>
       </c>
       <c r="L26" s="15">
-        <v>60.606060606060</v>
+        <v>50.649350649350</v>
       </c>
       <c r="M26" s="15">
-        <v>-30.718954248366</v>
+        <v>-28.395061728395</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,10 +1397,10 @@
         <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
         <v>7</v>
@@ -1412,7 +1412,7 @@
         <v>-30</v>
       </c>
       <c r="L27" s="15">
-        <v>40</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,20 +1428,20 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
         <v>8</v>
@@ -1453,7 +1453,7 @@
         <v>-20</v>
       </c>
       <c r="L28" s="15">
-        <v>-27.272727272727</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,32 +1466,32 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>4</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="14">
         <v>1</v>
       </c>
       <c r="E29" s="15">
-        <v>300</v>
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="I29" s="14">
         <v>6</v>
       </c>
       <c r="J29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K29" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="L29" s="15">
         <v>100</v>
@@ -1500,39 +1500,39 @@
         <v>-45.454545454545</v>
       </c>
       <c r="N29" s="15">
-        <v>-85.714285714285</v>
+        <v>-86.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>3</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="14">
         <v>1</v>
       </c>
       <c r="E30" s="15">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>300</v>
+        <v>50</v>
       </c>
       <c r="I30" s="14">
         <v>5</v>
       </c>
       <c r="J30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" s="15">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L30" s="15">
         <v>150</v>
@@ -1541,7 +1541,7 @@
         <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-86.842105263157</v>
+        <v>-87.804878048780</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-081pct.xlsx
+++ b/data/source/weekly/cs-en-us-081pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -901,14 +901,14 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="14">
-        <v>1</v>
-      </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>0</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
         <v>7</v>
@@ -923,10 +923,10 @@
         <v>75</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="N15" s="15">
-        <v>-68.181818181818</v>
+        <v>-69.565217391304</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
         <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>166.666666666667</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G16" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>85.714285714285</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="J16" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K16" s="15">
-        <v>42.307692307692</v>
+        <v>34.482758620689</v>
       </c>
       <c r="L16" s="15">
-        <v>19.354838709677</v>
+        <v>21.875</v>
       </c>
       <c r="M16" s="15">
-        <v>-41.269841269841</v>
+        <v>-42.647058823529</v>
       </c>
       <c r="N16" s="15">
-        <v>-86.738351254480</v>
+        <v>-87.254901960784</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="F17" s="14">
         <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="H17" s="15">
-        <v>4.347826086956</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="J17" s="14">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K17" s="15">
-        <v>16.071428571428</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L17" s="15">
-        <v>-5.797101449275</v>
+        <v>-1.408450704225</v>
       </c>
       <c r="M17" s="15">
-        <v>-2.985074626865</v>
+        <v>0</v>
       </c>
       <c r="N17" s="15">
-        <v>-63.687150837988</v>
+        <v>-63.350785340314</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,7 +1016,7 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>20</v>
@@ -1025,31 +1025,31 @@
         <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G18" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>12.5</v>
+        <v>60</v>
       </c>
       <c r="I18" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J18" s="14">
         <v>31</v>
       </c>
       <c r="K18" s="15">
-        <v>22.580645161290</v>
+        <v>25.806451612903</v>
       </c>
       <c r="L18" s="15">
-        <v>65.217391304347</v>
+        <v>44.444444444444</v>
       </c>
       <c r="M18" s="15">
-        <v>-11.627906976744</v>
+        <v>-11.363636363636</v>
       </c>
       <c r="N18" s="15">
-        <v>-75</v>
+        <v>-76.646706586826</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D19" s="14">
         <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>-33.333333333333</v>
+        <v>83.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G19" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H19" s="15">
-        <v>43.75</v>
+        <v>44.444444444444</v>
       </c>
       <c r="I19" s="14">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="J19" s="14">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="K19" s="15">
-        <v>20.689655172413</v>
+        <v>26.5625</v>
       </c>
       <c r="L19" s="15">
-        <v>12.903225806451</v>
+        <v>24.615384615384</v>
       </c>
       <c r="M19" s="15">
-        <v>7.692307692307</v>
+        <v>12.5</v>
       </c>
       <c r="N19" s="15">
-        <v>-14.634146341463</v>
+        <v>-7.954545454545</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F20" s="14">
+        <v>9</v>
+      </c>
+      <c r="G20" s="14">
         <v>8</v>
       </c>
-      <c r="G20" s="14">
-        <v>7</v>
-      </c>
       <c r="H20" s="15">
-        <v>14.285714285714</v>
+        <v>12.5</v>
       </c>
       <c r="I20" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J20" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K20" s="15">
-        <v>-9.523809523809</v>
+        <v>-12.5</v>
       </c>
       <c r="L20" s="15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M20" s="15">
-        <v>-17.391304347826</v>
+        <v>-16</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.333333333333</v>
+        <v>-87.116564417177</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
         <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>25</v>
+        <v>18.75</v>
       </c>
       <c r="F21" s="17">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G21" s="17">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H21" s="18">
-        <v>23.809523809523</v>
+        <v>41.379310344827</v>
       </c>
       <c r="I21" s="17">
-        <v>236</v>
+        <v>257</v>
       </c>
       <c r="J21" s="17">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="K21" s="18">
-        <v>16.256157635468</v>
+        <v>17.351598173516</v>
       </c>
       <c r="L21" s="18">
-        <v>12.918660287081</v>
+        <v>16.818181818181</v>
       </c>
       <c r="M21" s="18">
-        <v>-13.553113553113</v>
+        <v>-12.286689419795</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.904707233065</v>
+        <v>-72.832980972515</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,11 +1182,11 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>-100</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="13" t="s">
         <v>20</v>
@@ -1207,10 +1207,10 @@
         <v>40</v>
       </c>
       <c r="L22" s="15">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="M22" s="15">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G23" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H23" s="15">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I23" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J23" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K23" s="15">
-        <v>-30</v>
+        <v>-29.032258064516</v>
       </c>
       <c r="L23" s="15">
-        <v>-12.5</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="M23" s="15">
-        <v>5</v>
+        <v>4.761904761904</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D24" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="F24" s="14">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G24" s="14">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="H24" s="15">
-        <v>9.302325581395</v>
+        <v>-6.25</v>
       </c>
       <c r="I24" s="14">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="J24" s="14">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="K24" s="15">
-        <v>14.814814814814</v>
+        <v>7.894736842105</v>
       </c>
       <c r="L24" s="15">
-        <v>-8.823529411764</v>
+        <v>-15.025906735751</v>
       </c>
       <c r="M24" s="15">
-        <v>0.649350649350</v>
+        <v>-1.796407185628</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="14">
-        <v>2</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F25" s="14">
+        <v>4</v>
+      </c>
+      <c r="G25" s="14">
+        <v>4</v>
+      </c>
+      <c r="H25" s="15">
         <v>0</v>
-      </c>
-      <c r="F25" s="14">
-        <v>5</v>
-      </c>
-      <c r="G25" s="14">
-        <v>3</v>
-      </c>
-      <c r="H25" s="15">
-        <v>66.666666666666</v>
       </c>
       <c r="I25" s="14">
         <v>24</v>
       </c>
       <c r="J25" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K25" s="15">
-        <v>84.615384615384</v>
+        <v>71.428571428571</v>
       </c>
       <c r="L25" s="15">
-        <v>-25</v>
+        <v>-31.428571428571</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E26" s="15">
-        <v>80</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G26" s="14">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H26" s="15">
-        <v>95.652173913043</v>
+        <v>37.5</v>
       </c>
       <c r="I26" s="14">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J26" s="14">
-        <v>83</v>
+        <v>95</v>
       </c>
       <c r="K26" s="15">
-        <v>39.759036144578</v>
+        <v>27.368421052631</v>
       </c>
       <c r="L26" s="15">
-        <v>50.649350649350</v>
+        <v>34.444444444444</v>
       </c>
       <c r="M26" s="15">
-        <v>-28.395061728395</v>
+        <v>-30.057803468208</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1393,14 +1393,14 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="14">
-        <v>1</v>
-      </c>
-      <c r="G27" s="14">
-        <v>2</v>
-      </c>
-      <c r="H27" s="15">
-        <v>-50</v>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
         <v>7</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-50</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="I28" s="14">
         <v>8</v>
       </c>
       <c r="J28" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L28" s="15">
         <v>-33.333333333333</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
         <v>4</v>
@@ -1500,7 +1500,7 @@
         <v>-45.454545454545</v>
       </c>
       <c r="N29" s="15">
-        <v>-86.666666666666</v>
+        <v>-88.679245283018</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>3</v>
@@ -1541,7 +1541,7 @@
         <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-87.804878048780</v>
+        <v>-89.795918367346</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-081pct.xlsx
+++ b/data/source/weekly/cs-en-us-081pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -901,8 +901,8 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="F15" s="14">
+        <v>1</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -911,22 +911,22 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J15" s="14">
         <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>-22.222222222222</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L15" s="15">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="M15" s="15">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-69.565217391304</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="F16" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G16" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H16" s="15">
-        <v>66.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J16" s="14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K16" s="15">
-        <v>34.482758620689</v>
+        <v>23.529411764705</v>
       </c>
       <c r="L16" s="15">
-        <v>21.875</v>
+        <v>20</v>
       </c>
       <c r="M16" s="15">
-        <v>-42.647058823529</v>
+        <v>-40.845070422535</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.254901960784</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="F17" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G17" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H17" s="15">
-        <v>33.333333333333</v>
+        <v>5</v>
       </c>
       <c r="I17" s="14">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="J17" s="14">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="K17" s="15">
-        <v>16.666666666666</v>
+        <v>12.307692307692</v>
       </c>
       <c r="L17" s="15">
-        <v>-1.408450704225</v>
+        <v>-6.410256410256</v>
       </c>
       <c r="M17" s="15">
-        <v>0</v>
+        <v>-8.75</v>
       </c>
       <c r="N17" s="15">
-        <v>-63.350785340314</v>
+        <v>-65.238095238095</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,38 +1018,38 @@
       <c r="C18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H18" s="15">
-        <v>60</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J18" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K18" s="15">
-        <v>25.806451612903</v>
+        <v>25</v>
       </c>
       <c r="L18" s="15">
-        <v>44.444444444444</v>
+        <v>21.212121212121</v>
       </c>
       <c r="M18" s="15">
-        <v>-11.363636363636</v>
+        <v>-20</v>
       </c>
       <c r="N18" s="15">
-        <v>-76.646706586826</v>
+        <v>-77.777777777777</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>83.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="F19" s="14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G19" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H19" s="15">
-        <v>44.444444444444</v>
+        <v>31.578947368421</v>
       </c>
       <c r="I19" s="14">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="J19" s="14">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="K19" s="15">
-        <v>26.5625</v>
+        <v>18.571428571428</v>
       </c>
       <c r="L19" s="15">
-        <v>24.615384615384</v>
+        <v>15.277777777777</v>
       </c>
       <c r="M19" s="15">
-        <v>12.5</v>
+        <v>9.210526315789</v>
       </c>
       <c r="N19" s="15">
-        <v>-7.954545454545</v>
+        <v>-13.541666666666</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>2</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
         <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H20" s="15">
-        <v>12.5</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="14">
         <v>21</v>
       </c>
       <c r="J20" s="14">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="K20" s="15">
-        <v>-12.5</v>
+        <v>-25</v>
       </c>
       <c r="L20" s="15">
         <v>5</v>
       </c>
       <c r="M20" s="15">
-        <v>-16</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.116564417177</v>
+        <v>-88.397790055248</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>12</v>
+      </c>
+      <c r="D21" s="17">
         <v>19</v>
       </c>
-      <c r="D21" s="17">
-        <v>16</v>
-      </c>
       <c r="E21" s="18">
-        <v>18.75</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="F21" s="17">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="G21" s="17">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="H21" s="18">
-        <v>41.379310344827</v>
+        <v>14.0625</v>
       </c>
       <c r="I21" s="17">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="J21" s="17">
-        <v>219</v>
+        <v>240</v>
       </c>
       <c r="K21" s="18">
-        <v>17.351598173516</v>
+        <v>11.25</v>
       </c>
       <c r="L21" s="18">
-        <v>16.818181818181</v>
+        <v>9.876543209876</v>
       </c>
       <c r="M21" s="18">
-        <v>-12.286689419795</v>
+        <v>-16.037735849056</v>
       </c>
       <c r="N21" s="18">
-        <v>-72.832980972515</v>
+        <v>-74.202898550724</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1192,7 +1192,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H22" s="15">
         <v>-100</v>
@@ -1210,7 +1210,7 @@
         <v>40</v>
       </c>
       <c r="M22" s="15">
-        <v>0</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1230,28 +1230,28 @@
         <v>0</v>
       </c>
       <c r="F23" s="14">
+        <v>7</v>
+      </c>
+      <c r="G23" s="14">
         <v>9</v>
       </c>
-      <c r="G23" s="14">
-        <v>8</v>
-      </c>
       <c r="H23" s="15">
-        <v>12.5</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I23" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J23" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K23" s="15">
-        <v>-29.032258064516</v>
+        <v>-28.125</v>
       </c>
       <c r="L23" s="15">
-        <v>-15.384615384615</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="M23" s="15">
-        <v>4.761904761904</v>
+        <v>-4.166666666666</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>10</v>
       </c>
       <c r="D24" s="14">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E24" s="15">
-        <v>-41.176470588235</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F24" s="14">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G24" s="14">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H24" s="15">
-        <v>-6.25</v>
+        <v>-10.638297872340</v>
       </c>
       <c r="I24" s="14">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="J24" s="14">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="K24" s="15">
-        <v>7.894736842105</v>
+        <v>8.75</v>
       </c>
       <c r="L24" s="15">
-        <v>-15.025906735751</v>
+        <v>-16.346153846153</v>
       </c>
       <c r="M24" s="15">
-        <v>-1.796407185628</v>
+        <v>-0.571428571428</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
+      <c r="C25" s="14">
+        <v>2</v>
       </c>
       <c r="D25" s="14">
         <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F25" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G25" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H25" s="15">
         <v>0</v>
       </c>
       <c r="I25" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J25" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K25" s="15">
-        <v>71.428571428571</v>
+        <v>73.333333333333</v>
       </c>
       <c r="L25" s="15">
-        <v>-31.428571428571</v>
+        <v>-25.714285714285</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>-66.666666666666</v>
+        <v>-25</v>
       </c>
       <c r="F26" s="14">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G26" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H26" s="15">
-        <v>37.5</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="I26" s="14">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="J26" s="14">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="K26" s="15">
-        <v>27.368421052631</v>
+        <v>23.300970873786</v>
       </c>
       <c r="L26" s="15">
-        <v>34.444444444444</v>
+        <v>28.282828282828</v>
       </c>
       <c r="M26" s="15">
-        <v>-30.057803468208</v>
+        <v>-31.351351351351</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1393,8 +1393,8 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="F27" s="14">
+        <v>1</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1403,16 +1403,16 @@
         <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J27" s="14">
         <v>10</v>
       </c>
       <c r="K27" s="15">
-        <v>-30</v>
+        <v>-20</v>
       </c>
       <c r="L27" s="15">
-        <v>16.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
         <v>2</v>
       </c>
-      <c r="E28" s="15">
-        <v>-50</v>
-      </c>
-      <c r="F28" s="14">
-        <v>1</v>
-      </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>-75</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J28" s="14">
         <v>12</v>
       </c>
       <c r="K28" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="L28" s="15">
-        <v>-33.333333333333</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,10 +1497,10 @@
         <v>100</v>
       </c>
       <c r="M29" s="15">
-        <v>-45.454545454545</v>
+        <v>-62.5</v>
       </c>
       <c r="N29" s="15">
-        <v>-88.679245283018</v>
+        <v>-89.090909090909</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1538,10 +1538,10 @@
         <v>150</v>
       </c>
       <c r="M30" s="15">
-        <v>-50</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="N30" s="15">
-        <v>-89.795918367346</v>
+        <v>-90.196078431372</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-081pct.xlsx
+++ b/data/source/weekly/cs-en-us-081pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -923,10 +923,10 @@
         <v>100</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N15" s="15">
-        <v>-66.666666666666</v>
+        <v>-72.413793103448</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,10 +937,10 @@
         <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-40</v>
+        <v>200</v>
       </c>
       <c r="F16" s="14">
         <v>16</v>
@@ -952,22 +952,22 @@
         <v>33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="J16" s="14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K16" s="15">
-        <v>23.529411764705</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L16" s="15">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="M16" s="15">
-        <v>-40.845070422535</v>
+        <v>-42.307692307692</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.5</v>
+        <v>-87.671232876712</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-40</v>
+        <v>125</v>
       </c>
       <c r="F17" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H17" s="15">
-        <v>5</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="J17" s="14">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="K17" s="15">
-        <v>12.307692307692</v>
+        <v>21.739130434782</v>
       </c>
       <c r="L17" s="15">
-        <v>-6.410256410256</v>
+        <v>-5.617977528089</v>
       </c>
       <c r="M17" s="15">
-        <v>-8.75</v>
+        <v>0</v>
       </c>
       <c r="N17" s="15">
-        <v>-65.238095238095</v>
+        <v>-62.831858407079</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1028,28 +1028,28 @@
         <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" s="15">
-        <v>66.666666666666</v>
+        <v>150</v>
       </c>
       <c r="I18" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J18" s="14">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K18" s="15">
-        <v>25</v>
+        <v>24.242424242424</v>
       </c>
       <c r="L18" s="15">
-        <v>21.212121212121</v>
+        <v>20.588235294117</v>
       </c>
       <c r="M18" s="15">
-        <v>-20</v>
+        <v>-22.641509433962</v>
       </c>
       <c r="N18" s="15">
-        <v>-77.777777777777</v>
+        <v>-79.081632653061</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19" s="14">
+        <v>6</v>
+      </c>
+      <c r="E19" s="15">
+        <v>-50</v>
+      </c>
+      <c r="F19" s="14">
+        <v>18</v>
+      </c>
+      <c r="G19" s="14">
+        <v>25</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-28</v>
+      </c>
+      <c r="I19" s="14">
+        <v>84</v>
+      </c>
+      <c r="J19" s="14">
+        <v>77</v>
+      </c>
+      <c r="K19" s="15">
+        <v>9.090909090909</v>
+      </c>
+      <c r="L19" s="15">
+        <v>7.692307692307</v>
+      </c>
+      <c r="M19" s="15">
         <v>5</v>
       </c>
-      <c r="E19" s="15">
-        <v>-20</v>
-      </c>
-      <c r="F19" s="14">
-        <v>25</v>
-      </c>
-      <c r="G19" s="14">
-        <v>19</v>
-      </c>
-      <c r="H19" s="15">
-        <v>31.578947368421</v>
-      </c>
-      <c r="I19" s="14">
-        <v>83</v>
-      </c>
-      <c r="J19" s="14">
-        <v>70</v>
-      </c>
-      <c r="K19" s="15">
-        <v>18.571428571428</v>
-      </c>
-      <c r="L19" s="15">
-        <v>15.277777777777</v>
-      </c>
-      <c r="M19" s="15">
-        <v>9.210526315789</v>
-      </c>
       <c r="N19" s="15">
-        <v>-13.541666666666</v>
+        <v>-14.285714285714</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="14">
-        <v>3</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="C20" s="14">
+        <v>4</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G20" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H20" s="15">
-        <v>-50</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="I20" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J20" s="14">
         <v>28</v>
       </c>
       <c r="K20" s="15">
-        <v>-25</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="L20" s="15">
-        <v>5</v>
+        <v>8.695652173913</v>
       </c>
       <c r="M20" s="15">
-        <v>-22.222222222222</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N20" s="15">
-        <v>-88.397790055248</v>
+        <v>-87.179487179487</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>20</v>
+      </c>
+      <c r="D21" s="17">
         <v>12</v>
       </c>
-      <c r="D21" s="17">
-        <v>19</v>
-      </c>
       <c r="E21" s="18">
-        <v>-36.842105263157</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G21" s="17">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="H21" s="18">
-        <v>14.0625</v>
+        <v>7.575757575757</v>
       </c>
       <c r="I21" s="17">
-        <v>267</v>
+        <v>287</v>
       </c>
       <c r="J21" s="17">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="K21" s="18">
-        <v>11.25</v>
+        <v>13.438735177865</v>
       </c>
       <c r="L21" s="18">
-        <v>9.876543209876</v>
+        <v>8.301886792452</v>
       </c>
       <c r="M21" s="18">
-        <v>-16.037735849056</v>
+        <v>-16.081871345029</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.202898550724</v>
+        <v>-74.329159212880</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1188,29 +1188,29 @@
       <c r="E22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J22" s="14">
         <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="L22" s="15">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="M22" s="15">
-        <v>-22.222222222222</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
-      </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
-      <c r="E23" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G23" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H23" s="15">
-        <v>-22.222222222222</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I23" s="14">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J23" s="14">
         <v>32</v>
       </c>
       <c r="K23" s="15">
-        <v>-28.125</v>
+        <v>-18.75</v>
       </c>
       <c r="L23" s="15">
-        <v>-20.689655172413</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M23" s="15">
-        <v>-4.166666666666</v>
+        <v>4</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="D24" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E24" s="15">
-        <v>11.111111111111</v>
+        <v>50</v>
       </c>
       <c r="F24" s="14">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="G24" s="14">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="H24" s="15">
-        <v>-10.638297872340</v>
+        <v>3.921568627450</v>
       </c>
       <c r="I24" s="14">
-        <v>174</v>
+        <v>193</v>
       </c>
       <c r="J24" s="14">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="K24" s="15">
-        <v>8.75</v>
+        <v>12.209302325581</v>
       </c>
       <c r="L24" s="15">
-        <v>-16.346153846153</v>
+        <v>-13.452914798206</v>
       </c>
       <c r="M24" s="15">
-        <v>-0.571428571428</v>
+        <v>0.520833333333</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>1</v>
+      </c>
+      <c r="D25" s="14">
         <v>2</v>
       </c>
-      <c r="D25" s="14">
-        <v>1</v>
-      </c>
       <c r="E25" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
         <v>5</v>
       </c>
       <c r="G25" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H25" s="15">
-        <v>0</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J25" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K25" s="15">
-        <v>73.333333333333</v>
+        <v>58.823529411764</v>
       </c>
       <c r="L25" s="15">
-        <v>-25.714285714285</v>
+        <v>-22.857142857142</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="E26" s="15">
-        <v>-25</v>
+        <v>175</v>
       </c>
       <c r="F26" s="14">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G26" s="14">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="H26" s="15">
-        <v>-5.882352941176</v>
+        <v>0</v>
       </c>
       <c r="I26" s="14">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="J26" s="14">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="K26" s="15">
-        <v>23.300970873786</v>
+        <v>27.102803738317</v>
       </c>
       <c r="L26" s="15">
-        <v>28.282828282828</v>
+        <v>27.102803738317</v>
       </c>
       <c r="M26" s="15">
-        <v>-31.351351351351</v>
+        <v>-30.612244897959</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1412,7 +1412,7 @@
         <v>-20</v>
       </c>
       <c r="L27" s="15">
-        <v>33.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1438,10 +1438,10 @@
         <v>2</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
         <v>9</v>
@@ -1475,14 +1475,14 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>4</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>6</v>
@@ -1494,13 +1494,13 @@
         <v>50</v>
       </c>
       <c r="L29" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M29" s="15">
-        <v>-62.5</v>
+        <v>-68.421052631578</v>
       </c>
       <c r="N29" s="15">
-        <v>-89.090909090909</v>
+        <v>-89.830508474576</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1516,14 +1516,14 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>3</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>5</v>
@@ -1535,13 +1535,13 @@
         <v>66.666666666666</v>
       </c>
       <c r="L30" s="15">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M30" s="15">
-        <v>-61.538461538461</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="N30" s="15">
-        <v>-90.196078431372</v>
+        <v>-90.740740740740</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-081pct.xlsx
+++ b/data/source/weekly/cs-en-us-081pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -692,7 +692,7 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,7 +902,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -911,22 +911,22 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
         <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>-11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="M15" s="15">
-        <v>-11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="N15" s="15">
-        <v>-72.413793103448</v>
+        <v>-70.967741935483</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F16" s="14">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G16" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>33.333333333333</v>
+        <v>-10</v>
       </c>
       <c r="I16" s="14">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J16" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K16" s="15">
-        <v>28.571428571428</v>
+        <v>27.777777777777</v>
       </c>
       <c r="L16" s="15">
-        <v>25</v>
+        <v>17.948717948717</v>
       </c>
       <c r="M16" s="15">
-        <v>-42.307692307692</v>
+        <v>-45.882352941176</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.671232876712</v>
+        <v>-87.989556135770</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>125</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G17" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H17" s="15">
-        <v>33.333333333333</v>
+        <v>10.526315789473</v>
       </c>
       <c r="I17" s="14">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="J17" s="14">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="K17" s="15">
-        <v>21.739130434782</v>
+        <v>17.333333333333</v>
       </c>
       <c r="L17" s="15">
-        <v>-5.617977528089</v>
+        <v>-7.368421052631</v>
       </c>
       <c r="M17" s="15">
         <v>0</v>
       </c>
       <c r="N17" s="15">
-        <v>-62.831858407079</v>
+        <v>-63.025210084033</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H18" s="15">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="I18" s="14">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J18" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K18" s="15">
-        <v>24.242424242424</v>
+        <v>28.571428571428</v>
       </c>
       <c r="L18" s="15">
-        <v>20.588235294117</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M18" s="15">
-        <v>-22.641509433962</v>
+        <v>-22.413793103448</v>
       </c>
       <c r="N18" s="15">
-        <v>-79.081632653061</v>
+        <v>-78.971962616822</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>-50</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F19" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G19" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H19" s="15">
-        <v>-28</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="I19" s="14">
+        <v>90</v>
+      </c>
+      <c r="J19" s="14">
         <v>84</v>
       </c>
-      <c r="J19" s="14">
-        <v>77</v>
-      </c>
       <c r="K19" s="15">
-        <v>9.090909090909</v>
+        <v>7.142857142857</v>
       </c>
       <c r="L19" s="15">
-        <v>7.692307692307</v>
+        <v>7.142857142857</v>
       </c>
       <c r="M19" s="15">
-        <v>5</v>
+        <v>8.433734939759</v>
       </c>
       <c r="N19" s="15">
-        <v>-14.285714285714</v>
+        <v>-10</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>4</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G20" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H20" s="15">
-        <v>-22.222222222222</v>
+        <v>-25</v>
       </c>
       <c r="I20" s="14">
         <v>25</v>
       </c>
       <c r="J20" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K20" s="15">
-        <v>-10.714285714285</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="L20" s="15">
-        <v>8.695652173913</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="M20" s="15">
-        <v>-16.666666666666</v>
+        <v>-21.875</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.179487179487</v>
+        <v>-87.980769230769</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>66.666666666666</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="F21" s="17">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="G21" s="17">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H21" s="18">
-        <v>7.575757575757</v>
+        <v>-2.985074626865</v>
       </c>
       <c r="I21" s="17">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="J21" s="17">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="K21" s="18">
-        <v>13.438735177865</v>
+        <v>12.222222222222</v>
       </c>
       <c r="L21" s="18">
-        <v>8.301886792452</v>
+        <v>6.690140845070</v>
       </c>
       <c r="M21" s="18">
-        <v>-16.081871345029</v>
+        <v>-16.528925619834</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.329159212880</v>
+        <v>-74.387151310228</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1191,11 +1191,11 @@
       <c r="F22" s="14">
         <v>1</v>
       </c>
-      <c r="G22" s="14">
-        <v>1</v>
-      </c>
-      <c r="H22" s="15">
-        <v>0</v>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>8</v>
@@ -1210,7 +1210,7 @@
         <v>60</v>
       </c>
       <c r="M22" s="15">
-        <v>-11.111111111111</v>
+        <v>-20</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,35 +1223,35 @@
       <c r="C23" s="14">
         <v>2</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="D23" s="14">
+        <v>3</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-33.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H23" s="15">
-        <v>33.333333333333</v>
+        <v>40</v>
       </c>
       <c r="I23" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J23" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K23" s="15">
-        <v>-18.75</v>
+        <v>-20</v>
       </c>
       <c r="L23" s="15">
-        <v>-13.333333333333</v>
+        <v>-15.151515151515</v>
       </c>
       <c r="M23" s="15">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D24" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E24" s="15">
+        <v>20</v>
+      </c>
+      <c r="F24" s="14">
         <v>50</v>
       </c>
-      <c r="F24" s="14">
-        <v>53</v>
-      </c>
       <c r="G24" s="14">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="H24" s="15">
-        <v>3.921568627450</v>
+        <v>6.382978723404</v>
       </c>
       <c r="I24" s="14">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="J24" s="14">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="K24" s="15">
-        <v>12.209302325581</v>
+        <v>10.989010989011</v>
       </c>
       <c r="L24" s="15">
-        <v>-13.452914798206</v>
+        <v>-14.767932489451</v>
       </c>
       <c r="M24" s="15">
-        <v>0.520833333333</v>
+        <v>-3.349282296650</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="14">
-        <v>1</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F25" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G25" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H25" s="15">
-        <v>-16.666666666666</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I25" s="14">
         <v>27</v>
       </c>
       <c r="J25" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K25" s="15">
-        <v>58.823529411764</v>
+        <v>35</v>
       </c>
       <c r="L25" s="15">
-        <v>-22.857142857142</v>
+        <v>-27.027027027027</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D26" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="F26" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G26" s="14">
         <v>29</v>
       </c>
       <c r="H26" s="15">
-        <v>0</v>
+        <v>6.896551724137</v>
       </c>
       <c r="I26" s="14">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="J26" s="14">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="K26" s="15">
-        <v>27.102803738317</v>
+        <v>32.142857142857</v>
       </c>
       <c r="L26" s="15">
-        <v>27.102803738317</v>
+        <v>27.586206896551</v>
       </c>
       <c r="M26" s="15">
-        <v>-30.612244897959</v>
+        <v>-29.857819905213</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,7 +1394,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1403,16 +1403,16 @@
         <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J27" s="14">
         <v>10</v>
       </c>
       <c r="K27" s="15">
-        <v>-20</v>
+        <v>-10</v>
       </c>
       <c r="L27" s="15">
-        <v>14.285714285714</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
         <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J28" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>-25</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="L28" s="15">
-        <v>-30.769230769230</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,17 +1469,17 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>3</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29" s="15">
         <v>-100</v>
@@ -1488,10 +1488,10 @@
         <v>6</v>
       </c>
       <c r="J29" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K29" s="15">
-        <v>50</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L29" s="15">
         <v>50</v>
@@ -1500,7 +1500,7 @@
         <v>-68.421052631578</v>
       </c>
       <c r="N29" s="15">
-        <v>-89.830508474576</v>
+        <v>-90.476190476190</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,17 +1510,17 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>2</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
         <v>-100</v>
@@ -1529,10 +1529,10 @@
         <v>5</v>
       </c>
       <c r="J30" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K30" s="15">
-        <v>66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L30" s="15">
         <v>66.666666666666</v>
@@ -1541,7 +1541,7 @@
         <v>-64.285714285714</v>
       </c>
       <c r="N30" s="15">
-        <v>-90.740740740740</v>
+        <v>-91.379310344827</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1557,8 +1557,8 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
+      <c r="F31" s="14">
+        <v>1</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1566,8 +1566,8 @@
       <c r="H31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
+      <c r="I31" s="14">
+        <v>1</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-081pct.xlsx
+++ b/data/source/weekly/cs-en-us-081pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -902,7 +902,7 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -911,22 +911,22 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J15" s="14">
         <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>0</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L15" s="15">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="M15" s="15">
-        <v>0</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="N15" s="15">
-        <v>-70.967741935483</v>
+        <v>-68.75</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>3</v>
+      </c>
+      <c r="D16" s="14">
         <v>2</v>
       </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="F16" s="14">
+        <v>10</v>
+      </c>
+      <c r="G16" s="14">
         <v>9</v>
       </c>
-      <c r="G16" s="14">
-        <v>10</v>
-      </c>
       <c r="H16" s="15">
-        <v>-10</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I16" s="14">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J16" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K16" s="15">
-        <v>27.777777777777</v>
+        <v>28.947368421052</v>
       </c>
       <c r="L16" s="15">
-        <v>17.948717948717</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M16" s="15">
-        <v>-45.882352941176</v>
+        <v>-47.872340425531</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.989556135770</v>
+        <v>-87.931034482758</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>-37.5</v>
       </c>
       <c r="F17" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G17" s="14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="H17" s="15">
-        <v>10.526315789473</v>
+        <v>4.347826086956</v>
       </c>
       <c r="I17" s="14">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="J17" s="14">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="K17" s="15">
-        <v>17.333333333333</v>
+        <v>13.253012048192</v>
       </c>
       <c r="L17" s="15">
-        <v>-7.368421052631</v>
+        <v>-7.843137254901</v>
       </c>
       <c r="M17" s="15">
         <v>0</v>
       </c>
       <c r="N17" s="15">
-        <v>-63.025210084033</v>
+        <v>-64.122137404580</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
         <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="I18" s="14">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J18" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K18" s="15">
-        <v>28.571428571428</v>
+        <v>27.777777777777</v>
       </c>
       <c r="L18" s="15">
-        <v>28.571428571428</v>
+        <v>27.777777777777</v>
       </c>
       <c r="M18" s="15">
-        <v>-22.413793103448</v>
+        <v>-23.333333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-78.971962616822</v>
+        <v>-79.735682819383</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
         <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>-28.571428571428</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F19" s="14">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G19" s="14">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H19" s="15">
-        <v>-23.076923076923</v>
+        <v>-40</v>
       </c>
       <c r="I19" s="14">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="J19" s="14">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="K19" s="15">
-        <v>7.142857142857</v>
+        <v>2.197802197802</v>
       </c>
       <c r="L19" s="15">
-        <v>7.142857142857</v>
+        <v>1.086956521739</v>
       </c>
       <c r="M19" s="15">
-        <v>8.433734939759</v>
+        <v>5.681818181818</v>
       </c>
       <c r="N19" s="15">
-        <v>-10</v>
+        <v>-13.084112149532</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
+        <v>5</v>
+      </c>
+      <c r="G20" s="14">
         <v>6</v>
       </c>
-      <c r="G20" s="14">
-        <v>8</v>
-      </c>
       <c r="H20" s="15">
-        <v>-25</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I20" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J20" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K20" s="15">
-        <v>-13.793103448275</v>
+        <v>-16.129032258064</v>
       </c>
       <c r="L20" s="15">
-        <v>-3.846153846153</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="M20" s="15">
-        <v>-21.875</v>
+        <v>-18.75</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.980769230769</v>
+        <v>-87.619047619047</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
+        <v>-25</v>
+      </c>
+      <c r="F21" s="17">
+        <v>64</v>
+      </c>
+      <c r="G21" s="17">
+        <v>68</v>
+      </c>
+      <c r="H21" s="18">
         <v>-5.882352941176</v>
       </c>
-      <c r="F21" s="17">
-        <v>65</v>
-      </c>
-      <c r="G21" s="17">
-        <v>67</v>
-      </c>
-      <c r="H21" s="18">
-        <v>-2.985074626865</v>
-      </c>
       <c r="I21" s="17">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="J21" s="17">
-        <v>270</v>
+        <v>290</v>
       </c>
       <c r="K21" s="18">
-        <v>12.222222222222</v>
+        <v>9.655172413793</v>
       </c>
       <c r="L21" s="18">
-        <v>6.690140845070</v>
+        <v>3.921568627450</v>
       </c>
       <c r="M21" s="18">
-        <v>-16.528925619834</v>
+        <v>-17.829457364341</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.387151310228</v>
+        <v>-74.641148325358</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>1</v>
       </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="G22" s="14">
+        <v>1</v>
+      </c>
+      <c r="H22" s="15">
+        <v>0</v>
       </c>
       <c r="I22" s="14">
         <v>8</v>
       </c>
       <c r="J22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K22" s="15">
-        <v>60</v>
+        <v>33.333333333333</v>
       </c>
       <c r="L22" s="15">
         <v>60</v>
       </c>
       <c r="M22" s="15">
-        <v>-20</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E23" s="15">
-        <v>-33.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="F23" s="14">
         <v>7</v>
       </c>
       <c r="G23" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H23" s="15">
-        <v>40</v>
+        <v>-12.5</v>
       </c>
       <c r="I23" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J23" s="14">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K23" s="15">
-        <v>-20</v>
+        <v>-25.641025641025</v>
       </c>
       <c r="L23" s="15">
-        <v>-15.151515151515</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="M23" s="15">
-        <v>12</v>
+        <v>11.538461538461</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D24" s="14">
         <v>10</v>
       </c>
       <c r="E24" s="15">
-        <v>20</v>
+        <v>90</v>
       </c>
       <c r="F24" s="14">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G24" s="14">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="H24" s="15">
-        <v>6.382978723404</v>
+        <v>39.024390243902</v>
       </c>
       <c r="I24" s="14">
-        <v>202</v>
+        <v>221</v>
       </c>
       <c r="J24" s="14">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="K24" s="15">
-        <v>10.989010989011</v>
+        <v>15.104166666666</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.767932489451</v>
+        <v>-10.887096774193</v>
       </c>
       <c r="M24" s="15">
-        <v>-3.349282296650</v>
+        <v>-2.212389380530</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
+      <c r="C25" s="14">
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="F25" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G25" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H25" s="15">
-        <v>-57.142857142857</v>
+        <v>-25</v>
       </c>
       <c r="I25" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J25" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K25" s="15">
-        <v>35</v>
+        <v>36.363636363636</v>
       </c>
       <c r="L25" s="15">
-        <v>-27.027027027027</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="F26" s="14">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="G26" s="14">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H26" s="15">
-        <v>6.896551724137</v>
+        <v>51.851851851851</v>
       </c>
       <c r="I26" s="14">
-        <v>148</v>
+        <v>162</v>
       </c>
       <c r="J26" s="14">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="K26" s="15">
-        <v>32.142857142857</v>
+        <v>32.786885245901</v>
       </c>
       <c r="L26" s="15">
-        <v>27.586206896551</v>
+        <v>22.727272727272</v>
       </c>
       <c r="M26" s="15">
-        <v>-29.857819905213</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1394,7 +1394,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1403,16 +1403,16 @@
         <v>21</v>
       </c>
       <c r="I27" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J27" s="14">
         <v>10</v>
       </c>
       <c r="K27" s="15">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="L27" s="15">
-        <v>28.571428571428</v>
+        <v>42.857142857142</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1438,22 +1438,22 @@
         <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I28" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J28" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K28" s="15">
-        <v>-23.076923076923</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="L28" s="15">
-        <v>-23.076923076923</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>3</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1500,7 +1500,7 @@
         <v>-68.421052631578</v>
       </c>
       <c r="N29" s="15">
-        <v>-90.476190476190</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>2</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1541,7 +1541,7 @@
         <v>-64.285714285714</v>
       </c>
       <c r="N30" s="15">
-        <v>-91.379310344827</v>
+        <v>-92.1875</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>0</v>
       </c>
       <c r="I31" s="14">
         <v>1</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>0</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-081pct.xlsx
+++ b/data/source/weekly/cs-en-us-081pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -869,41 +869,41 @@
       <c r="H14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="14">
         <v>2</v>
       </c>
       <c r="K14" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L14" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="M14" s="15">
-        <v>-100</v>
+        <v>-87.5</v>
       </c>
       <c r="N14" s="15">
-        <v>-100</v>
+        <v>-90</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <v>3</v>
-      </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
       </c>
@@ -911,22 +911,22 @@
         <v>21</v>
       </c>
       <c r="I15" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
         <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>150</v>
+        <v>125</v>
       </c>
       <c r="M15" s="15">
-        <v>-9.090909090909</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="N15" s="15">
-        <v>-68.75</v>
+        <v>-72.727272727272</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E16" s="15">
-        <v>50</v>
+        <v>-20</v>
       </c>
       <c r="F16" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16" s="14">
         <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>11.111111111111</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I16" s="14">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J16" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K16" s="15">
-        <v>28.947368421052</v>
+        <v>23.255813953488</v>
       </c>
       <c r="L16" s="15">
-        <v>16.666666666666</v>
+        <v>23.255813953488</v>
       </c>
       <c r="M16" s="15">
-        <v>-47.872340425531</v>
+        <v>-45.918367346938</v>
       </c>
       <c r="N16" s="15">
-        <v>-87.931034482758</v>
+        <v>-87.645687645687</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,10 +978,10 @@
         <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>-37.5</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
         <v>24</v>
@@ -993,63 +993,63 @@
         <v>4.347826086956</v>
       </c>
       <c r="I17" s="14">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="J17" s="14">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="K17" s="15">
-        <v>13.253012048192</v>
+        <v>12.5</v>
       </c>
       <c r="L17" s="15">
-        <v>-7.843137254901</v>
+        <v>-6.603773584905</v>
       </c>
       <c r="M17" s="15">
-        <v>0</v>
+        <v>-1.980198019801</v>
       </c>
       <c r="N17" s="15">
-        <v>-64.122137404580</v>
+        <v>-65.140845070422</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G18" s="14">
         <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I18" s="14">
         <v>46</v>
       </c>
       <c r="J18" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K18" s="15">
-        <v>27.777777777777</v>
+        <v>24.324324324324</v>
       </c>
       <c r="L18" s="15">
-        <v>27.777777777777</v>
+        <v>24.324324324324</v>
       </c>
       <c r="M18" s="15">
-        <v>-23.333333333333</v>
+        <v>-30.303030303030</v>
       </c>
       <c r="N18" s="15">
-        <v>-79.735682819383</v>
+        <v>-80.991735537190</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>-42.857142857142</v>
+        <v>-37.5</v>
       </c>
       <c r="F19" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G19" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="H19" s="15">
-        <v>-40</v>
+        <v>-39.285714285714</v>
       </c>
       <c r="I19" s="14">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="J19" s="14">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="K19" s="15">
-        <v>2.197802197802</v>
+        <v>-1.010101010101</v>
       </c>
       <c r="L19" s="15">
-        <v>1.086956521739</v>
+        <v>-1.010101010101</v>
       </c>
       <c r="M19" s="15">
-        <v>5.681818181818</v>
+        <v>5.376344086021</v>
       </c>
       <c r="N19" s="15">
-        <v>-13.084112149532</v>
+        <v>-11.711711711711</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="14">
         <v>2</v>
       </c>
-      <c r="E20" s="15">
-        <v>-50</v>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G20" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>-16.666666666666</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J20" s="14">
         <v>31</v>
       </c>
       <c r="K20" s="15">
-        <v>-16.129032258064</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="L20" s="15">
-        <v>-10.344827586206</v>
+        <v>-12.5</v>
       </c>
       <c r="M20" s="15">
-        <v>-18.75</v>
+        <v>-20</v>
       </c>
       <c r="N20" s="15">
-        <v>-87.619047619047</v>
+        <v>-87.443946188340</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>-25</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="F21" s="17">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G21" s="17">
         <v>68</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.882352941176</v>
+        <v>-1.470588235294</v>
       </c>
       <c r="I21" s="17">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="J21" s="17">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="K21" s="18">
-        <v>9.655172413793</v>
+        <v>8.090614886731</v>
       </c>
       <c r="L21" s="18">
-        <v>3.921568627450</v>
+        <v>3.726708074534</v>
       </c>
       <c r="M21" s="18">
-        <v>-17.829457364341</v>
+        <v>-18.932038834951</v>
       </c>
       <c r="N21" s="18">
-        <v>-74.641148325358</v>
+        <v>-74.924924924924</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>2</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F22" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I22" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K22" s="15">
-        <v>33.333333333333</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L22" s="15">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="M22" s="15">
-        <v>-27.272727272727</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="F23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G23" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H23" s="15">
-        <v>-12.5</v>
+        <v>-20</v>
       </c>
       <c r="I23" s="14">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J23" s="14">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K23" s="15">
-        <v>-25.641025641025</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="L23" s="15">
-        <v>-23.684210526315</v>
+        <v>-17.948717948717</v>
       </c>
       <c r="M23" s="15">
-        <v>11.538461538461</v>
+        <v>14.285714285714</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D24" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E24" s="15">
-        <v>90</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F24" s="14">
         <v>57</v>
       </c>
       <c r="G24" s="14">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H24" s="15">
-        <v>39.024390243902</v>
+        <v>23.913043478260</v>
       </c>
       <c r="I24" s="14">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="J24" s="14">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="K24" s="15">
-        <v>15.104166666666</v>
+        <v>12.135922330097</v>
       </c>
       <c r="L24" s="15">
-        <v>-10.887096774193</v>
+        <v>-11.153846153846</v>
       </c>
       <c r="M24" s="15">
-        <v>-2.212389380530</v>
+        <v>-0.858369098712</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="14">
-        <v>3</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="F25" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G25" s="14">
         <v>8</v>
       </c>
       <c r="H25" s="15">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="I25" s="14">
         <v>30</v>
       </c>
       <c r="J25" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K25" s="15">
-        <v>36.363636363636</v>
+        <v>30.434782608695</v>
       </c>
       <c r="L25" s="15">
-        <v>-23.076923076923</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
         <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>60</v>
+        <v>-30</v>
       </c>
       <c r="F26" s="14">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G26" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H26" s="15">
-        <v>51.851851851851</v>
+        <v>51.724137931034</v>
       </c>
       <c r="I26" s="14">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="J26" s="14">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="K26" s="15">
-        <v>32.786885245901</v>
+        <v>28.030303030303</v>
       </c>
       <c r="L26" s="15">
-        <v>22.727272727272</v>
+        <v>16.551724137931</v>
       </c>
       <c r="M26" s="15">
-        <v>-30.769230769230</v>
+        <v>-32.936507936507</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,7 +1394,7 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1425,23 +1425,23 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
         <v>11</v>
@@ -1453,7 +1453,7 @@
         <v>-21.428571428571</v>
       </c>
       <c r="L28" s="15">
-        <v>-26.666666666666</v>
+        <v>-31.25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-68.421052631578</v>
       </c>
       <c r="N29" s="15">
-        <v>-91.666666666666</v>
+        <v>-92.207792207792</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>-64.285714285714</v>
       </c>
       <c r="N30" s="15">
-        <v>-92.1875</v>
+        <v>-92.753623188405</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="14">
         <v>1</v>
